--- a/results/manual_eval_qwen7B_rag_validation.xlsx
+++ b/results/manual_eval_qwen7B_rag_validation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YADEL\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\RAG\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84C2E03-2861-4525-A19C-6D5617111F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913919A9-E944-406A-9947-06A9D9A5F78A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="1068" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
